--- a/basedatos_partidas/salida/descompuestos/07.04.02.030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.02.030.xlsx
@@ -584,10 +584,10 @@
         <v>0.55</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="12">
@@ -636,10 +636,10 @@
         <v>0.55</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>3.96</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="14">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>108.8</v>
+        <v>109.35</v>
       </c>
     </row>
     <row r="15">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>138.78</v>
+        <v>139.33</v>
       </c>
       <c r="H25" t="n">
         <v>1.39</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>140.17</v>
+        <v>140.72</v>
       </c>
     </row>
   </sheetData>
